--- a/private/intl/pe/sueldo-y-liquidacion-2026.xlsx
+++ b/private/intl/pe/sueldo-y-liquidacion-2026.xlsx
@@ -1601,7 +1601,7 @@
       <formula1>"Sí: un sueldo cada una,Sí: medio sueldo cada una,No recibo gratificaciones"</formula1>
     </dataValidation>
     <dataValidation type="list" showErrorMessage="1" error="Elige una opción de la lista." sqref="B11">
-      <formula1>"EsSalud,EPS (entidad prestadora de salud)"</formula1>
+      <formula1>'Tablas oficiales'!$B$8:$B$9</formula1>
     </dataValidation>
     <dataValidation type="decimal" allowBlank="1" showErrorMessage="1" error="Escribe un número mayor o igual a 0." sqref="B5">
       <formula1>0</formula1>
@@ -1614,7 +1614,7 @@
       <formula1>"AFP (sistema privado),ONP (sistema nacional)"</formula1>
     </dataValidation>
     <dataValidation type="list" showErrorMessage="1" error="Elige una opción de la lista." sqref="B8">
-      <formula1>"AFP Habitat,AFP Integra,Prima AFP,Profuturo AFP"</formula1>
+      <formula1>'Tablas oficiales'!$B$4:$B$7</formula1>
     </dataValidation>
     <dataValidation type="list" showErrorMessage="1" error="Elige una opción de la lista." sqref="B9">
       <formula1>"Sobre el saldo (mixta),Sobre el sueldo (flujo)"</formula1>
@@ -1918,7 +1918,7 @@
       <formula2>6</formula2>
     </dataValidation>
     <dataValidation type="list" showErrorMessage="1" error="Elige una opción de la lista." sqref="B12">
-      <formula1>"EsSalud,EPS (entidad prestadora de salud)"</formula1>
+      <formula1>'Tablas oficiales'!$B$8:$B$9</formula1>
     </dataValidation>
     <dataValidation type="decimal" allowBlank="1" showErrorMessage="1" error="Escribe un número mayor o igual a 0." sqref="B22">
       <formula1>0</formula1>
@@ -2420,7 +2420,7 @@
       <formula2>120</formula2>
     </dataValidation>
     <dataValidation type="list" showErrorMessage="1" error="Elige una opción de la lista." sqref="B13">
-      <formula1>"EsSalud,EPS (entidad prestadora de salud)"</formula1>
+      <formula1>'Tablas oficiales'!$B$8:$B$9</formula1>
     </dataValidation>
     <dataValidation type="list" showErrorMessage="1" error="Elige una opción de la lista." sqref="B31">
       <formula1>"A plazo indeterminado,A plazo fijo (con fecha de fin)"</formula1>

--- a/private/intl/pe/sueldo-y-liquidacion-2026.xlsx
+++ b/private/intl/pe/sueldo-y-liquidacion-2026.xlsx
@@ -32,7 +32,7 @@
     <t>«Liquidación»: pones tus fechas y tu sueldo, y te dice la CTS trunca, la gratificación trunca, las vacaciones y, si te despidieron sin causa, la indemnización.</t>
   </si>
   <si>
-    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 8/10/2026.</t>
+    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 9/10/2026.</t>
   </si>
   <si>
     <t>Cuando cambia un valor oficial, actualizamos la planilla y el mismo enlace de descarga te baja la versión nueva.</t>
@@ -413,7 +413,7 @@
     <t>Tablas oficiales de Perú</t>
   </si>
   <si>
-    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 8/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
+    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 9/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
   </si>
   <si>
     <t>Dato</t>
@@ -2013,7 +2013,7 @@
         <v>88</v>
       </c>
       <c r="B6" s="20">
-        <v>46303</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">

--- a/private/intl/pe/sueldo-y-liquidacion-2026.xlsx
+++ b/private/intl/pe/sueldo-y-liquidacion-2026.xlsx
@@ -32,7 +32,7 @@
     <t>«Liquidación»: pones tus fechas y tu sueldo, y te dice la CTS trunca, la gratificación trunca, las vacaciones y, si te despidieron sin causa, la indemnización.</t>
   </si>
   <si>
-    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 9/10/2026.</t>
+    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 13/10/2026.</t>
   </si>
   <si>
     <t>Cuando cambia un valor oficial, actualizamos la planilla y el mismo enlace de descarga te baja la versión nueva.</t>
@@ -413,7 +413,7 @@
     <t>Tablas oficiales de Perú</t>
   </si>
   <si>
-    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 9/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
+    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 13/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
   </si>
   <si>
     <t>Dato</t>
@@ -2013,7 +2013,7 @@
         <v>88</v>
       </c>
       <c r="B6" s="20">
-        <v>46304</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">

--- a/private/intl/pe/sueldo-y-liquidacion-2026.xlsx
+++ b/private/intl/pe/sueldo-y-liquidacion-2026.xlsx
@@ -32,7 +32,7 @@
     <t>«Liquidación»: pones tus fechas y tu sueldo, y te dice la CTS trunca, la gratificación trunca, las vacaciones y, si te despidieron sin causa, la indemnización.</t>
   </si>
   <si>
-    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 9/10/2026.</t>
+    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 14/10/2026.</t>
   </si>
   <si>
     <t>Cuando cambia un valor oficial, actualizamos la planilla y el mismo enlace de descarga te baja la versión nueva.</t>
@@ -413,7 +413,7 @@
     <t>Tablas oficiales de Perú</t>
   </si>
   <si>
-    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 9/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
+    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 14/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
   </si>
   <si>
     <t>Dato</t>
@@ -2013,7 +2013,7 @@
         <v>88</v>
       </c>
       <c r="B6" s="20">
-        <v>46304</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">

--- a/private/intl/pe/sueldo-y-liquidacion-2026.xlsx
+++ b/private/intl/pe/sueldo-y-liquidacion-2026.xlsx
@@ -32,7 +32,7 @@
     <t>«Liquidación»: pones tus fechas y tu sueldo, y te dice la CTS trunca, la gratificación trunca, las vacaciones y, si te despidieron sin causa, la indemnización.</t>
   </si>
   <si>
-    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 14/10/2026.</t>
+    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 15/10/2026.</t>
   </si>
   <si>
     <t>Cuando cambia un valor oficial, actualizamos la planilla y el mismo enlace de descarga te baja la versión nueva.</t>
@@ -413,7 +413,7 @@
     <t>Tablas oficiales de Perú</t>
   </si>
   <si>
-    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 14/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
+    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 15/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
   </si>
   <si>
     <t>Dato</t>
@@ -2013,7 +2013,7 @@
         <v>88</v>
       </c>
       <c r="B6" s="20">
-        <v>46309</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">

--- a/private/intl/pe/sueldo-y-liquidacion-2026.xlsx
+++ b/private/intl/pe/sueldo-y-liquidacion-2026.xlsx
@@ -32,7 +32,7 @@
     <t>«Liquidación»: pones tus fechas y tu sueldo, y te dice la CTS trunca, la gratificación trunca, las vacaciones y, si te despidieron sin causa, la indemnización.</t>
   </si>
   <si>
-    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 15/10/2026.</t>
+    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 16/10/2026.</t>
   </si>
   <si>
     <t>Cuando cambia un valor oficial, actualizamos la planilla y el mismo enlace de descarga te baja la versión nueva.</t>
@@ -413,7 +413,7 @@
     <t>Tablas oficiales de Perú</t>
   </si>
   <si>
-    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 15/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
+    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 16/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
   </si>
   <si>
     <t>Dato</t>
@@ -2013,7 +2013,7 @@
         <v>88</v>
       </c>
       <c r="B6" s="20">
-        <v>46310</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">

--- a/private/intl/pe/sueldo-y-liquidacion-2026.xlsx
+++ b/private/intl/pe/sueldo-y-liquidacion-2026.xlsx
@@ -32,7 +32,7 @@
     <t>«Liquidación»: pones tus fechas y tu sueldo, y te dice la CTS trunca, la gratificación trunca, las vacaciones y, si te despidieron sin causa, la indemnización.</t>
   </si>
   <si>
-    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 16/10/2026.</t>
+    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 19/10/2026.</t>
   </si>
   <si>
     <t>Cuando cambia un valor oficial, actualizamos la planilla y el mismo enlace de descarga te baja la versión nueva.</t>
@@ -413,7 +413,7 @@
     <t>Tablas oficiales de Perú</t>
   </si>
   <si>
-    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 16/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
+    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 19/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
   </si>
   <si>
     <t>Dato</t>
@@ -2013,7 +2013,7 @@
         <v>88</v>
       </c>
       <c r="B6" s="20">
-        <v>46311</v>
+        <v>46314</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">

--- a/private/intl/pe/sueldo-y-liquidacion-2026.xlsx
+++ b/private/intl/pe/sueldo-y-liquidacion-2026.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="189">
   <si>
     <t>Planilla de sueldo y liquidación Perú 2026</t>
   </si>
@@ -32,7 +32,7 @@
     <t>«Liquidación»: pones tus fechas y tu sueldo, y te dice la CTS trunca, la gratificación trunca, las vacaciones y, si te despidieron sin causa, la indemnización.</t>
   </si>
   <si>
-    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 19/10/2026.</t>
+    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 20/10/2026.</t>
   </si>
   <si>
     <t>Cuando cambia un valor oficial, actualizamos la planilla y el mismo enlace de descarga te baja la versión nueva.</t>
@@ -50,18 +50,33 @@
     <t>Sueldo neto: AFP u ONP y renta de quinta</t>
   </si>
   <si>
+    <t>AFP Habitat</t>
+  </si>
+  <si>
+    <t>AFP Integra</t>
+  </si>
+  <si>
     <t>Paso a paso</t>
   </si>
   <si>
+    <t>Prima AFP</t>
+  </si>
+  <si>
     <t>TUS DATOS</t>
   </si>
   <si>
+    <t>Profuturo AFP</t>
+  </si>
+  <si>
     <t>Sueldo mensual bruto</t>
   </si>
   <si>
     <t>Pensión</t>
   </si>
   <si>
+    <t>EsSalud</t>
+  </si>
+  <si>
     <t>Cobras asignación familiar</t>
   </si>
   <si>
@@ -71,6 +86,9 @@
     <t>Asignación familiar</t>
   </si>
   <si>
+    <t>EPS (entidad prestadora de salud)</t>
+  </si>
+  <si>
     <t>Sistema de pensiones</t>
   </si>
   <si>
@@ -83,9 +101,6 @@
     <t>Tu AFP</t>
   </si>
   <si>
-    <t>AFP Habitat</t>
-  </si>
-  <si>
     <t>Aporte a la ONP</t>
   </si>
   <si>
@@ -116,9 +131,6 @@
     <t>Tu seguro de salud</t>
   </si>
   <si>
-    <t>EsSalud</t>
-  </si>
-  <si>
     <t>Comisión sobre el sueldo (%)</t>
   </si>
   <si>
@@ -413,7 +425,7 @@
     <t>Tablas oficiales de Perú</t>
   </si>
   <si>
-    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 19/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
+    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 20/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
   </si>
   <si>
     <t>Dato</t>
@@ -452,15 +464,6 @@
     <t>7/10/2026</t>
   </si>
   <si>
-    <t>AFP Integra</t>
-  </si>
-  <si>
-    <t>Prima AFP</t>
-  </si>
-  <si>
-    <t>Profuturo AFP</t>
-  </si>
-  <si>
     <t>Bonificación extraordinaria sobre la gratificación</t>
   </si>
   <si>
@@ -468,9 +471,6 @@
   </si>
   <si>
     <t>https://cdn.www.gob.pe/uploads/document/file/3321103/guia_gratificaciones.pdf</t>
-  </si>
-  <si>
-    <t>EPS (entidad prestadora de salud)</t>
   </si>
   <si>
     <t>Unidad impositiva tributaria</t>
@@ -1287,7 +1287,7 @@
   <sheetPr>
     <tabColor rgb="FF1B5E20"/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:Z26"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
@@ -1296,62 +1296,83 @@
     <col min="4" max="4" width="3" customWidth="1"/>
     <col min="5" max="5" width="50" customWidth="1"/>
     <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="26" max="26" width="9" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" ht="28" customHeight="1" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>10</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
-    </row>
-    <row r="3" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="Z1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="26:26" x14ac:dyDescent="0.25">
+      <c r="Z2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="5:26" x14ac:dyDescent="0.25">
       <c r="E3" s="6" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F3" s="6"/>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="Z3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="Z4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B5" s="8">
         <v>3000</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F6" s="12">
         <f>IF(B6="Sí",ROUND('Tablas oficiales'!$C$11*'Tablas oficiales'!$C$12/100,2),0)</f>
       </c>
+      <c r="Z6" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F7" s="12">
         <f>ROUND(B5+F6,2)</f>
@@ -1359,13 +1380,13 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F8" s="12">
         <f>IF(B7="AFP (sistema privado)",0,ROUND(F7*'Tablas oficiales'!$C$13/100,2))</f>
@@ -1373,16 +1394,16 @@
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F9" s="12">
         <f>IF(B7="AFP (sistema privado)",ROUND(F7*'Tablas oficiales'!$C$14/100,2),0)</f>
@@ -1390,16 +1411,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="F10" s="12">
         <f>IF(B7="AFP (sistema privado)",ROUND(MIN(F7,'Tablas oficiales'!$C$15)*'Tablas oficiales'!$C$16/100,2),0)</f>
@@ -1407,13 +1428,13 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F11" s="14">
         <f>IF(B9="Sobre el sueldo (flujo)",INDEX('Tablas oficiales'!$C$4:$C$7,MATCH(B8,'Tablas oficiales'!$B$4:$B$7,0)),'Tablas oficiales'!$C$17)</f>
@@ -1421,7 +1442,7 @@
     </row>
     <row r="12" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E12" s="11" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F12" s="12">
         <f>IF(B7="AFP (sistema privado)",ROUND(F7*F11/100,2),0)</f>
@@ -1429,12 +1450,12 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
       <c r="E13" s="11" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F13" s="12">
         <f>ROUND(F8+F9+F10+F12,2)</f>
@@ -1442,7 +1463,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="15" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B14" s="16">
         <f>F7</f>
@@ -1450,24 +1471,24 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="15" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="B15" s="16">
         <f>F8</f>
       </c>
       <c r="E15" s="9" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="15" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B16" s="16">
         <f>F9</f>
       </c>
       <c r="E16" s="11" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F16" s="12">
         <f>ROUND(F7*IF(B10="Sí: un sueldo cada una",2,IF(B10="Sí: medio sueldo cada una",1,0)),2)</f>
@@ -1475,13 +1496,13 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="15" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="B17" s="16">
         <f>F10</f>
       </c>
       <c r="E17" s="11" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F17" s="12">
         <f>ROUND(F16*INDEX('Tablas oficiales'!$C$8:$C$9,MATCH(B11,'Tablas oficiales'!$B$8:$B$9,0))/100,2)</f>
@@ -1489,13 +1510,13 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="15" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B18" s="16">
         <f>F12</f>
       </c>
       <c r="E18" s="11" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F18" s="12">
         <f>ROUND(F7*12+F16+F17,2)</f>
@@ -1503,13 +1524,13 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="15" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B19" s="16">
         <f>F13</f>
       </c>
       <c r="E19" s="11" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F19" s="12">
         <f>MAX(0,ROUND(F18-'Tablas oficiales'!$C$18*'Tablas oficiales'!$C$10,2))</f>
@@ -1517,13 +1538,13 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="15" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B20" s="16">
         <f>F26</f>
       </c>
       <c r="E20" s="11" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="F20" s="12">
         <f>MAX(0,MIN(F19,'Tablas oficiales'!$C$21*'Tablas oficiales'!$C$10)-'Tablas oficiales'!$B$21*'Tablas oficiales'!$C$10)*'Tablas oficiales'!$D$21/100</f>
@@ -1531,13 +1552,13 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="17" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B21" s="18">
         <f>ROUND(F7-F13-F26,2)</f>
       </c>
       <c r="E21" s="11" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F21" s="12">
         <f>MAX(0,MIN(F19,'Tablas oficiales'!$C$22*'Tablas oficiales'!$C$10)-'Tablas oficiales'!$B$22*'Tablas oficiales'!$C$10)*'Tablas oficiales'!$D$22/100</f>
@@ -1545,7 +1566,7 @@
     </row>
     <row r="22" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E22" s="11" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F22" s="12">
         <f>MAX(0,MIN(F19,'Tablas oficiales'!$C$23*'Tablas oficiales'!$C$10)-'Tablas oficiales'!$B$23*'Tablas oficiales'!$C$10)*'Tablas oficiales'!$D$23/100</f>
@@ -1553,12 +1574,12 @@
     </row>
     <row r="23" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
       <c r="E23" s="11" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="F23" s="12">
         <f>MAX(0,MIN(F19,'Tablas oficiales'!$C$24*'Tablas oficiales'!$C$10)-'Tablas oficiales'!$B$24*'Tablas oficiales'!$C$10)*'Tablas oficiales'!$D$24/100</f>
@@ -1566,7 +1587,7 @@
     </row>
     <row r="24" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E24" s="11" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F24" s="12">
         <f>MAX(0,MIN(F19,'Tablas oficiales'!$C$25*'Tablas oficiales'!$C$10)-'Tablas oficiales'!$B$25*'Tablas oficiales'!$C$10)*'Tablas oficiales'!$D$25/100</f>
@@ -1574,7 +1595,7 @@
     </row>
     <row r="25" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E25" s="11" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="F25" s="12">
         <f>SUM(F20,F21,F22,F23,F24)</f>
@@ -1582,7 +1603,7 @@
     </row>
     <row r="26" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E26" s="11" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F26" s="12">
         <f>ROUND(ROUND(F25,2)/12,2)</f>
@@ -1600,8 +1621,8 @@
     <dataValidation type="list" showErrorMessage="1" error="Elige una opción de la lista." sqref="B10">
       <formula1>"Sí: un sueldo cada una,Sí: medio sueldo cada una,No recibo gratificaciones"</formula1>
     </dataValidation>
-    <dataValidation type="list" showErrorMessage="1" error="Elige una opción de la lista." sqref="B11">
-      <formula1>'Tablas oficiales'!$B$8:$B$9</formula1>
+    <dataValidation type="list" showErrorMessage="1" error="Elige una opción de la lista (Tu seguro de salud)." sqref="B11">
+      <formula1>'Sueldo neto'!$Z$5:$Z$6</formula1>
     </dataValidation>
     <dataValidation type="decimal" allowBlank="1" showErrorMessage="1" error="Escribe un número mayor o igual a 0." sqref="B5">
       <formula1>0</formula1>
@@ -1613,8 +1634,8 @@
     <dataValidation type="list" showErrorMessage="1" error="Elige una opción de la lista." sqref="B7">
       <formula1>"AFP (sistema privado),ONP (sistema nacional)"</formula1>
     </dataValidation>
-    <dataValidation type="list" showErrorMessage="1" error="Elige una opción de la lista." sqref="B8">
-      <formula1>'Tablas oficiales'!$B$4:$B$7</formula1>
+    <dataValidation type="list" showErrorMessage="1" error="Elige una opción de la lista (Tu AFP)." sqref="B8">
+      <formula1>'Sueldo neto'!$Z$1:$Z$4</formula1>
     </dataValidation>
     <dataValidation type="list" showErrorMessage="1" error="Elige una opción de la lista." sqref="B9">
       <formula1>"Sobre el saldo (mixta),Sobre el sueldo (flujo)"</formula1>
@@ -1630,7 +1651,7 @@
   <sheetPr>
     <tabColor rgb="FF1B5E20"/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:Z31"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
@@ -1639,29 +1660,38 @@
     <col min="4" max="4" width="3" customWidth="1"/>
     <col min="5" max="5" width="50" customWidth="1"/>
     <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="26" max="26" width="9" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" ht="28" customHeight="1" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
+      <c r="Z1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="26:26" x14ac:dyDescent="0.25">
+      <c r="Z2" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="3" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E3" s="6" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F3" s="6"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
       <c r="E4" s="11" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F4" s="12">
         <f>IF(B6="Sí",ROUND('Tablas oficiales'!$C$11*'Tablas oficiales'!$C$12/100,2),0)</f>
@@ -1669,36 +1699,36 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B5" s="8">
         <v>3000</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="13" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F7" s="12">
         <f>ROUND(B5+F4+IF(ISNUMBER(B7),B7,0),2)</f>
@@ -1706,13 +1736,13 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="E8" s="11" t="s">
         <v>62</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="E8" s="11" t="s">
-        <v>58</v>
       </c>
       <c r="F8" s="12">
         <f>IF(B8="Microempresa (REMYPE)",0,ROUND(F7*IF(B8="Régimen general",'Tablas oficiales'!$C$27,IF(B8="Pequeña empresa (REMYPE)",'Tablas oficiales'!$C$28,0))*B11/6,2))</f>
@@ -1720,7 +1750,7 @@
     </row>
     <row r="9" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E9" s="11" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="F9" s="12">
         <f>IF(B8="Microempresa (REMYPE)",0,ROUND(F8*INDEX('Tablas oficiales'!$C$8:$C$9,MATCH(B12,'Tablas oficiales'!$B$8:$B$9,0))/100,2))</f>
@@ -1728,31 +1758,31 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B10" s="6"/>
       <c r="C10" s="6"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B11" s="19">
         <v>6</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F12" s="12">
         <f>ROUND(IF(ISNUMBER(B22),B22,0)/6,2)</f>
@@ -1760,13 +1790,13 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="15" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B13" s="16">
         <f>F7</f>
       </c>
       <c r="E13" s="11" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F13" s="12">
         <f>ROUND(B5+F4+IF(ISNUMBER(B7),B7,0)+F12,2)</f>
@@ -1774,13 +1804,13 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="15" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="B14" s="16">
         <f>F4</f>
       </c>
       <c r="E14" s="11" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F14" s="12">
         <f>IF(B8="Microempresa (REMYPE)",0,ROUND(F13*IF(B8="Régimen general",'Tablas oficiales'!$C$29,IF(B8="Pequeña empresa (REMYPE)",'Tablas oficiales'!$C$30,0))/12*B23,2))</f>
@@ -1788,13 +1818,13 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="15" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B15" s="16">
         <f>F8</f>
       </c>
       <c r="E15" s="11" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="F15" s="12">
         <f>IF(B8="Microempresa (REMYPE)",0,ROUND(F13*IF(B8="Régimen general",'Tablas oficiales'!$C$29,IF(B8="Pequeña empresa (REMYPE)",'Tablas oficiales'!$C$30,0))/360*B24,2))</f>
@@ -1802,7 +1832,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="15" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="B16" s="16">
         <f>F9</f>
@@ -1810,7 +1840,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="17" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B17" s="18">
         <f>ROUND(F8+F9,2)</f>
@@ -1818,30 +1848,30 @@
     </row>
     <row r="19" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B21" s="6"/>
       <c r="C21" s="6"/>
     </row>
     <row r="22" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="B22" s="8"/>
       <c r="C22" s="13" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="B23" s="19">
         <v>6</v>
@@ -1849,7 +1879,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="B24" s="19">
         <v>0</v>
@@ -1857,7 +1887,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="15" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B25" s="16">
         <f>F13</f>
@@ -1865,7 +1895,7 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="15" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="B26" s="16">
         <f>F12</f>
@@ -1873,7 +1903,7 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="15" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="B27" s="16">
         <f>F14</f>
@@ -1881,7 +1911,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="15" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="B28" s="16">
         <f>F15</f>
@@ -1889,7 +1919,7 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="17" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B29" s="18">
         <f>ROUND(F14+F15,2)</f>
@@ -1897,7 +1927,7 @@
     </row>
     <row r="31" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
@@ -1917,8 +1947,8 @@
       <formula1>0</formula1>
       <formula2>6</formula2>
     </dataValidation>
-    <dataValidation type="list" showErrorMessage="1" error="Elige una opción de la lista." sqref="B12">
-      <formula1>'Tablas oficiales'!$B$8:$B$9</formula1>
+    <dataValidation type="list" showErrorMessage="1" error="Elige una opción de la lista (Tu seguro de salud)." sqref="B12">
+      <formula1>'Gratificación y CTS'!$Z$1:$Z$2</formula1>
     </dataValidation>
     <dataValidation type="decimal" allowBlank="1" showErrorMessage="1" error="Escribe un número mayor o igual a 0." sqref="B22">
       <formula1>0</formula1>
@@ -1957,7 +1987,7 @@
   <sheetPr>
     <tabColor rgb="FF1B5E20"/>
   </sheetPr>
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:Z42"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
@@ -1966,29 +1996,38 @@
     <col min="4" max="4" width="3" customWidth="1"/>
     <col min="5" max="5" width="50" customWidth="1"/>
     <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="26" max="26" width="9" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" ht="28" customHeight="1" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
+      <c r="Z1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="26:26" x14ac:dyDescent="0.25">
+      <c r="Z2" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="3" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E3" s="6" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F3" s="6"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
       <c r="E4" s="11" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F4" s="12">
         <f>IF(B8="Sí",ROUND('Tablas oficiales'!$C$11*'Tablas oficiales'!$C$12/100,2),0)</f>
@@ -1996,13 +2035,13 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B5" s="20">
         <v>44986</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F5" s="12">
         <f>ROUND(B7+F4+IF(ISNUMBER(B9),B9,0),2)</f>
@@ -2010,32 +2049,32 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B6" s="20">
-        <v>46314</v>
+        <v>46315</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B7" s="8">
         <v>3000</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="F8" s="21">
         <f>IF(B6&lt;B5,0,(YEAR((B6+1))-YEAR(B5))*12+MONTH((B6+1))-MONTH(B5)-IF(DAY((B6+1))&lt;DAY(B5),1,0))</f>
@@ -2043,14 +2082,14 @@
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B9" s="8"/>
       <c r="C9" s="13" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="F9" s="21">
         <f>INT(F8/12)</f>
@@ -2058,13 +2097,13 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F10" s="21">
         <f>MOD(F8,12)</f>
@@ -2072,14 +2111,14 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="B11" s="8"/>
       <c r="C11" s="13" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="F11" s="21">
         <f>IF(B6&lt;B5,0,MIN((B6+1)-DATE(YEAR(DATE(YEAR(B5),MONTH(B5)+F8,1)),MONTH(DATE(YEAR(B5),MONTH(B5)+F8,1)),MIN(DAY(B5),DAY(EOMONTH(DATE(YEAR(B5),MONTH(B5)+F8,1),0)))),29))</f>
@@ -2087,7 +2126,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="B12" s="19">
         <v>0</v>
@@ -2095,18 +2134,18 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="14" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E14" s="11" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="F14" s="21">
         <f>IF(DAY(MAX(B5,IF(MONTH(B6)&gt;=11,DATE(YEAR(B6),11,1),IF(MONTH(B6)&gt;=5,DATE(YEAR(B6),5,1),DATE(YEAR(B6)-1,11,1)))))=1,0,DAY(EOMONTH(MAX(B5,IF(MONTH(B6)&gt;=11,DATE(YEAR(B6),11,1),IF(MONTH(B6)&gt;=5,DATE(YEAR(B6),5,1),DATE(YEAR(B6)-1,11,1)))),0))-DAY(MAX(B5,IF(MONTH(B6)&gt;=11,DATE(YEAR(B6),11,1),IF(MONTH(B6)&gt;=5,DATE(YEAR(B6),5,1),DATE(YEAR(B6)-1,11,1)))))+1)+IF(DAY(B6)=DAY(EOMONTH(B6,0)),0,DAY(B6))</f>
@@ -2114,12 +2153,12 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B15" s="6"/>
       <c r="C15" s="6"/>
       <c r="E15" s="11" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="F15" s="21">
         <f>IF(B6&lt;MAX(B5,IF(MONTH(B6)&gt;=11,DATE(YEAR(B6),11,1),IF(MONTH(B6)&gt;=5,DATE(YEAR(B6),5,1),DATE(YEAR(B6)-1,11,1)))),0,IF(AND(YEAR(MAX(B5,IF(MONTH(B6)&gt;=11,DATE(YEAR(B6),11,1),IF(MONTH(B6)&gt;=5,DATE(YEAR(B6),5,1),DATE(YEAR(B6)-1,11,1)))))=YEAR(B6),MONTH(MAX(B5,IF(MONTH(B6)&gt;=11,DATE(YEAR(B6),11,1),IF(MONTH(B6)&gt;=5,DATE(YEAR(B6),5,1),DATE(YEAR(B6)-1,11,1)))))=MONTH(B6)),IF(AND(DAY(MAX(B5,IF(MONTH(B6)&gt;=11,DATE(YEAR(B6),11,1),IF(MONTH(B6)&gt;=5,DATE(YEAR(B6),5,1),DATE(YEAR(B6)-1,11,1)))))=1,DAY(B6)=DAY(EOMONTH(B6,0))),1,0),IF(DAY(MAX(B5,IF(MONTH(B6)&gt;=11,DATE(YEAR(B6),11,1),IF(MONTH(B6)&gt;=5,DATE(YEAR(B6),5,1),DATE(YEAR(B6)-1,11,1)))))=1,1,0)+IF(DAY(B6)=DAY(EOMONTH(B6,0)),1,0)+MAX(0,(YEAR(B6)*12+MONTH(B6))-(YEAR(MAX(B5,IF(MONTH(B6)&gt;=11,DATE(YEAR(B6),11,1),IF(MONTH(B6)&gt;=5,DATE(YEAR(B6),5,1),DATE(YEAR(B6)-1,11,1)))))*12+MONTH(MAX(B5,IF(MONTH(B6)&gt;=11,DATE(YEAR(B6),11,1),IF(MONTH(B6)&gt;=5,DATE(YEAR(B6),5,1),DATE(YEAR(B6)-1,11,1))))))-1)+INT(F14/30)))</f>
@@ -2132,7 +2171,7 @@
       <c r="B16" s="22"/>
       <c r="C16" s="22"/>
       <c r="E16" s="11" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="F16" s="21">
         <f>IF(B6&lt;MAX(B5,IF(MONTH(B6)&gt;=11,DATE(YEAR(B6),11,1),IF(MONTH(B6)&gt;=5,DATE(YEAR(B6),5,1),DATE(YEAR(B6)-1,11,1)))),0,IF(AND(YEAR(MAX(B5,IF(MONTH(B6)&gt;=11,DATE(YEAR(B6),11,1),IF(MONTH(B6)&gt;=5,DATE(YEAR(B6),5,1),DATE(YEAR(B6)-1,11,1)))))=YEAR(B6),MONTH(MAX(B5,IF(MONTH(B6)&gt;=11,DATE(YEAR(B6),11,1),IF(MONTH(B6)&gt;=5,DATE(YEAR(B6),5,1),DATE(YEAR(B6)-1,11,1)))))=MONTH(B6)),IF(AND(DAY(MAX(B5,IF(MONTH(B6)&gt;=11,DATE(YEAR(B6),11,1),IF(MONTH(B6)&gt;=5,DATE(YEAR(B6),5,1),DATE(YEAR(B6)-1,11,1)))))=1,DAY(B6)=DAY(EOMONTH(B6,0))),0,DAY(B6)-DAY(MAX(B5,IF(MONTH(B6)&gt;=11,DATE(YEAR(B6),11,1),IF(MONTH(B6)&gt;=5,DATE(YEAR(B6),5,1),DATE(YEAR(B6)-1,11,1)))))+1),MOD(F14,30)))</f>
@@ -2140,13 +2179,13 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="15" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B17" s="16">
         <f>F5</f>
       </c>
       <c r="E17" s="11" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="F17" s="12">
         <f>F5+ROUND(IF(ISNUMBER(B11),B11,0)/6,2)</f>
@@ -2154,13 +2193,13 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="15" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B18" s="16">
         <f>F18</f>
       </c>
       <c r="E18" s="11" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="F18" s="12">
         <f>IF(AND(NOT(B10="Microempresa (REMYPE)"),OR(F9&gt;0,F10&gt;0)),ROUND(F17*IF(B10="Régimen general",'Tablas oficiales'!$C$29,IF(B10="Pequeña empresa (REMYPE)",'Tablas oficiales'!$C$30,0))/12*F15+F17*IF(B10="Régimen general",'Tablas oficiales'!$C$29,IF(B10="Pequeña empresa (REMYPE)",'Tablas oficiales'!$C$30,0))/360*F16,2),0)</f>
@@ -2168,7 +2207,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="15" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="B19" s="16">
         <f>F22</f>
@@ -2176,24 +2215,24 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="15" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="B20" s="16">
         <f>F23</f>
       </c>
       <c r="E20" s="9" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="15" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B21" s="16">
         <f>F27</f>
       </c>
       <c r="E21" s="11" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="F21" s="21">
         <f>IF(B6&lt;MAX(B5,DATE(YEAR(B6),IF(MONTH(B6)&lt;=6,1,7),1)),0,MAX(0,IF(DAY(B6)=DAY(EOMONTH(B6,0)),(YEAR(B6)*12+MONTH(B6)),(YEAR(B6)*12+MONTH(B6))-1)-IF(DAY(MAX(B5,DATE(YEAR(B6),IF(MONTH(B6)&lt;=6,1,7),1)))=1,(YEAR(MAX(B5,DATE(YEAR(B6),IF(MONTH(B6)&lt;=6,1,7),1)))*12+MONTH(MAX(B5,DATE(YEAR(B6),IF(MONTH(B6)&lt;=6,1,7),1)))),(YEAR(MAX(B5,DATE(YEAR(B6),IF(MONTH(B6)&lt;=6,1,7),1)))*12+MONTH(MAX(B5,DATE(YEAR(B6),IF(MONTH(B6)&lt;=6,1,7),1))))+1)+1))</f>
@@ -2201,13 +2240,13 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="15" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="B22" s="16">
         <f>F28</f>
       </c>
       <c r="E22" s="11" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="F22" s="12">
         <f>IF(B10="Microempresa (REMYPE)",0,ROUND(F5*IF(B10="Régimen general",'Tablas oficiales'!$C$27,IF(B10="Pequeña empresa (REMYPE)",'Tablas oficiales'!$C$28,0))*F21/6,2))</f>
@@ -2215,13 +2254,13 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="17" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="B23" s="18">
         <f>ROUND(F18+F22+F23+F27+F28,2)</f>
       </c>
       <c r="E23" s="11" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="F23" s="12">
         <f>IF(B10="Microempresa (REMYPE)",0,ROUND(F22*INDEX('Tablas oficiales'!$C$8:$C$9,MATCH(B13,'Tablas oficiales'!$B$8:$B$9,0))/100,2))</f>
@@ -2229,7 +2268,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="15" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="B24" s="23">
         <f>F15</f>
@@ -2237,24 +2276,24 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="15" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="B25" s="23">
         <f>F16</f>
       </c>
       <c r="E25" s="9" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="15" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B26" s="23">
         <f>F21</f>
       </c>
       <c r="E26" s="11" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="F26" s="12">
         <f>F5*IF(B10="Régimen general",'Tablas oficiales'!$C$31,IF(B10="Pequeña empresa (REMYPE)",'Tablas oficiales'!$C$32,'Tablas oficiales'!$C$33))/30</f>
@@ -2262,7 +2301,7 @@
     </row>
     <row r="27" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E27" s="11" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="F27" s="12">
         <f>IF(OR(F9&gt;0,F10&gt;0),ROUND(F26/12*F10+F26/360*F11,2),0)</f>
@@ -2270,12 +2309,12 @@
     </row>
     <row r="28" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B28" s="4"/>
       <c r="C28" s="4"/>
       <c r="E28" s="11" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="F28" s="12">
         <f>ROUND(F5/30*B12,2)</f>
@@ -2283,23 +2322,23 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="B30" s="6"/>
       <c r="C30" s="6"/>
       <c r="E30" s="9" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F31" s="24">
         <f>IF(B31="A plazo fijo (con fecha de fin)",IF(B10="Régimen general",'Tablas oficiales'!$C$34,IF(B10="Pequeña empresa (REMYPE)",'Tablas oficiales'!$C$35,'Tablas oficiales'!$C$36))*B32+IF(B10="Régimen general",'Tablas oficiales'!$C$34,IF(B10="Pequeña empresa (REMYPE)",'Tablas oficiales'!$C$35,'Tablas oficiales'!$C$36))/30*B33,IF(B10="Régimen general",IF(B10="Régimen general",'Tablas oficiales'!$C$34,IF(B10="Pequeña empresa (REMYPE)",'Tablas oficiales'!$C$35,'Tablas oficiales'!$C$36))*(F9+F10/12+F11/360),IF(B10="Régimen general",'Tablas oficiales'!$C$34,IF(B10="Pequeña empresa (REMYPE)",'Tablas oficiales'!$C$35,'Tablas oficiales'!$C$36))*(F9+F10/12)))</f>
@@ -2307,16 +2346,16 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B32" s="19">
         <v>0</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="F32" s="24">
         <f>IF(AND(F9=0,F10&lt;3),0,MIN(F31,IF(B10="Régimen general",'Tablas oficiales'!$C$37,IF(B10="Pequeña empresa (REMYPE)",'Tablas oficiales'!$C$38,'Tablas oficiales'!$C$39))))</f>
@@ -2324,13 +2363,13 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="B33" s="19">
         <v>0</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -2342,7 +2381,7 @@
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="15" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="B35" s="16">
         <f>F5</f>
@@ -2350,7 +2389,7 @@
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="15" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="B36" s="23">
         <f>F9</f>
@@ -2358,7 +2397,7 @@
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="15" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B37" s="23">
         <f>F10</f>
@@ -2366,7 +2405,7 @@
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="15" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B38" s="23">
         <f>F11</f>
@@ -2374,7 +2413,7 @@
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="15" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B39" s="25">
         <f>ROUND(F32,2)</f>
@@ -2382,7 +2421,7 @@
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="17" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B40" s="18">
         <f>ROUND(F32*F5/30,2)</f>
@@ -2390,7 +2429,7 @@
     </row>
     <row r="42" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B42" s="4"/>
       <c r="C42" s="4"/>
@@ -2419,8 +2458,8 @@
       <formula1>0</formula1>
       <formula2>120</formula2>
     </dataValidation>
-    <dataValidation type="list" showErrorMessage="1" error="Elige una opción de la lista." sqref="B13">
-      <formula1>'Tablas oficiales'!$B$8:$B$9</formula1>
+    <dataValidation type="list" showErrorMessage="1" error="Elige una opción de la lista (Tu seguro de salud)." sqref="B13">
+      <formula1>'Liquidación'!$Z$1:$Z$2</formula1>
     </dataValidation>
     <dataValidation type="list" showErrorMessage="1" error="Elige una opción de la lista." sqref="B31">
       <formula1>"A plazo indeterminado,A plazo fijo (con fecha de fin)"</formula1>
@@ -2472,7 +2511,7 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="26" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B1" s="26"/>
       <c r="C1" s="26"/>
@@ -2483,7 +2522,7 @@
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -2494,163 +2533,163 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="27" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B3" s="27" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="C3" s="27" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="D3" s="27" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="E3" s="27" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="F3" s="27" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="G3" s="27" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="28" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B4" s="28" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="C4" s="29">
         <v>1.47</v>
       </c>
       <c r="D4" s="28" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="E4" s="28" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="F4" s="30" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="G4" s="28" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="31" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B5" s="31" t="s">
-        <v>145</v>
+        <v>12</v>
       </c>
       <c r="C5" s="32">
         <v>1.55</v>
       </c>
       <c r="D5" s="31" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="E5" s="31" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="F5" s="33" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="G5" s="31" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="28" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B6" s="28" t="s">
-        <v>146</v>
+        <v>14</v>
       </c>
       <c r="C6" s="29">
         <v>1.6</v>
       </c>
       <c r="D6" s="28" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="E6" s="28" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="F6" s="30" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="G6" s="28" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="31" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B7" s="31" t="s">
-        <v>147</v>
+        <v>16</v>
       </c>
       <c r="C7" s="32">
         <v>1.69</v>
       </c>
       <c r="D7" s="31" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="E7" s="31" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="F7" s="33" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="G7" s="31" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="28" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B8" s="28" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="C8" s="29">
         <v>9</v>
       </c>
       <c r="D8" s="28" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="E8" s="28" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F8" s="30" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G8" s="28" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="31" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B9" s="31" t="s">
-        <v>151</v>
+        <v>23</v>
       </c>
       <c r="C9" s="32">
         <v>6.75</v>
       </c>
       <c r="D9" s="31" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="E9" s="31" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F9" s="33" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G9" s="31" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -2673,7 +2712,7 @@
         <v>156</v>
       </c>
       <c r="G10" s="28" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -2690,18 +2729,18 @@
         <v>154</v>
       </c>
       <c r="E11" s="31" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="F11" s="33" t="s">
         <v>158</v>
       </c>
       <c r="G11" s="31" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="28" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="B12" s="28" t="s">
         <v>153</v>
@@ -2710,7 +2749,7 @@
         <v>10</v>
       </c>
       <c r="D12" s="28" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="E12" s="28" t="s">
         <v>159</v>
@@ -2719,7 +2758,7 @@
         <v>160</v>
       </c>
       <c r="G12" s="28" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -2733,7 +2772,7 @@
         <v>13</v>
       </c>
       <c r="D13" s="31" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="E13" s="31" t="s">
         <v>155</v>
@@ -2742,7 +2781,7 @@
         <v>162</v>
       </c>
       <c r="G13" s="31" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -2756,16 +2795,16 @@
         <v>10</v>
       </c>
       <c r="D14" s="28" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="E14" s="28" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="F14" s="30" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="G14" s="28" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -2782,13 +2821,13 @@
         <v>154</v>
       </c>
       <c r="E15" s="31" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="F15" s="33" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="G15" s="31" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -2802,16 +2841,16 @@
         <v>1.37</v>
       </c>
       <c r="D16" s="28" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="E16" s="28" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="F16" s="30" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="G16" s="28" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -2825,16 +2864,16 @@
         <v>0</v>
       </c>
       <c r="D17" s="31" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="E17" s="31" t="s">
         <v>167</v>
       </c>
       <c r="F17" s="33" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="G17" s="31" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -2857,7 +2896,7 @@
         <v>171</v>
       </c>
       <c r="G18" s="28" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -2876,7 +2915,7 @@
         <v>174</v>
       </c>
       <c r="G19" s="37" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.25">
@@ -2968,7 +3007,7 @@
         <v>179</v>
       </c>
       <c r="B27" s="31" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C27" s="32">
         <v>1</v>
@@ -2983,7 +3022,7 @@
         <v>160</v>
       </c>
       <c r="G27" s="31" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -3006,7 +3045,7 @@
         <v>160</v>
       </c>
       <c r="G28" s="28" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -3014,7 +3053,7 @@
         <v>183</v>
       </c>
       <c r="B29" s="31" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C29" s="32">
         <v>1</v>
@@ -3029,7 +3068,7 @@
         <v>160</v>
       </c>
       <c r="G29" s="31" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -3052,7 +3091,7 @@
         <v>160</v>
       </c>
       <c r="G30" s="28" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -3060,7 +3099,7 @@
         <v>184</v>
       </c>
       <c r="B31" s="31" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C31" s="32">
         <v>30</v>
@@ -3075,7 +3114,7 @@
         <v>160</v>
       </c>
       <c r="G31" s="31" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -3098,7 +3137,7 @@
         <v>160</v>
       </c>
       <c r="G32" s="28" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -3121,7 +3160,7 @@
         <v>160</v>
       </c>
       <c r="G33" s="31" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -3129,7 +3168,7 @@
         <v>187</v>
       </c>
       <c r="B34" s="28" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C34" s="29">
         <v>45</v>
@@ -3144,7 +3183,7 @@
         <v>160</v>
       </c>
       <c r="G34" s="28" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -3167,7 +3206,7 @@
         <v>160</v>
       </c>
       <c r="G35" s="31" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -3190,7 +3229,7 @@
         <v>160</v>
       </c>
       <c r="G36" s="28" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
@@ -3198,7 +3237,7 @@
         <v>188</v>
       </c>
       <c r="B37" s="31" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C37" s="32">
         <v>360</v>
@@ -3213,7 +3252,7 @@
         <v>160</v>
       </c>
       <c r="G37" s="31" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
@@ -3236,7 +3275,7 @@
         <v>160</v>
       </c>
       <c r="G38" s="28" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
@@ -3259,7 +3298,7 @@
         <v>160</v>
       </c>
       <c r="G39" s="31" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
   </sheetData>

--- a/private/intl/pe/sueldo-y-liquidacion-2026.xlsx
+++ b/private/intl/pe/sueldo-y-liquidacion-2026.xlsx
@@ -32,7 +32,7 @@
     <t>«Liquidación»: pones tus fechas y tu sueldo, y te dice la CTS trunca, la gratificación trunca, las vacaciones y, si te despidieron sin causa, la indemnización.</t>
   </si>
   <si>
-    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 20/10/2026.</t>
+    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 21/10/2026.</t>
   </si>
   <si>
     <t>Cuando cambia un valor oficial, actualizamos la planilla y el mismo enlace de descarga te baja la versión nueva.</t>
@@ -425,7 +425,7 @@
     <t>Tablas oficiales de Perú</t>
   </si>
   <si>
-    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 20/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
+    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 21/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
   </si>
   <si>
     <t>Dato</t>
@@ -2052,7 +2052,7 @@
         <v>92</v>
       </c>
       <c r="B6" s="20">
-        <v>46315</v>
+        <v>46316</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">

--- a/private/intl/pe/sueldo-y-liquidacion-2026.xlsx
+++ b/private/intl/pe/sueldo-y-liquidacion-2026.xlsx
@@ -32,7 +32,7 @@
     <t>«Liquidación»: pones tus fechas y tu sueldo, y te dice la CTS trunca, la gratificación trunca, las vacaciones y, si te despidieron sin causa, la indemnización.</t>
   </si>
   <si>
-    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 21/10/2026.</t>
+    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 22/10/2026.</t>
   </si>
   <si>
     <t>Cuando cambia un valor oficial, actualizamos la planilla y el mismo enlace de descarga te baja la versión nueva.</t>
@@ -425,7 +425,7 @@
     <t>Tablas oficiales de Perú</t>
   </si>
   <si>
-    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 21/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
+    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 22/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
   </si>
   <si>
     <t>Dato</t>
@@ -2052,7 +2052,7 @@
         <v>92</v>
       </c>
       <c r="B6" s="20">
-        <v>46316</v>
+        <v>46317</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
